--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5214,7 +5214,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>175</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5618,7 +5618,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>183</v>
       </c>
@@ -5633,13 +5633,13 @@
         <v>62</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5721,7 +5721,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>186</v>
       </c>
@@ -5736,13 +5736,13 @@
         <v>187</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>74</v>
@@ -6030,7 +6030,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>198</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
